--- a/curation/draft/package16/R16_BC_updates.xlsx
+++ b/curation/draft/package16/R16_BC_updates.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\_github\cdisc-org\COSMoS\curation\draft\package16\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cdisc-my.sharepoint.com/personal/jchason_cdisc_org/Documents/Work/CDISC/Biomedical Concepts/BCs for RE/files to send/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B90ECF83-A769-480E-B790-602DD1E4D64A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{8F5E3FC9-21B2-4A73-A801-FA9923351BFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="915" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="16663" windowHeight="9772" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BC_Updates" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="195" uniqueCount="92">
   <si>
     <t>update to released</t>
   </si>
@@ -298,6 +298,9 @@
   </si>
   <si>
     <t>Pulse Oximetry;Arterial Blood Gas (ABG) Stick</t>
+  </si>
+  <si>
+    <t>Respiratory System Findings</t>
   </si>
 </sst>
 </file>
@@ -691,29 +694,29 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:S19"/>
-  <sheetFormatPr defaultColWidth="40.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="40.69140625" defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="16.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="28.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.28515625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="13.5703125" style="1" customWidth="1"/>
-    <col min="6" max="6" width="40.7109375" style="1" customWidth="1"/>
-    <col min="7" max="7" width="39.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.28515625" style="1" customWidth="1"/>
-    <col min="9" max="9" width="40.7109375" style="1" customWidth="1"/>
-    <col min="10" max="10" width="9.85546875" style="1" customWidth="1"/>
-    <col min="11" max="11" width="13.5703125" style="1" customWidth="1"/>
-    <col min="12" max="12" width="6.7109375" style="1" customWidth="1"/>
-    <col min="13" max="13" width="6.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="15.28515625" style="1" customWidth="1"/>
-    <col min="15" max="15" width="18.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.140625" style="1" customWidth="1"/>
-    <col min="17" max="17" width="56.7109375" style="1" customWidth="1"/>
-    <col min="18" max="16384" width="40.7109375" style="1"/>
+    <col min="1" max="1" width="16.3828125" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.3046875" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.84375" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.3046875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="13.53515625" style="1" customWidth="1"/>
+    <col min="6" max="6" width="40.69140625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="39.53515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.3046875" style="1" customWidth="1"/>
+    <col min="9" max="9" width="40.69140625" style="1" customWidth="1"/>
+    <col min="10" max="10" width="9.84375" style="1" customWidth="1"/>
+    <col min="11" max="11" width="13.53515625" style="1" customWidth="1"/>
+    <col min="12" max="12" width="6.69140625" style="1" customWidth="1"/>
+    <col min="13" max="13" width="6.84375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="15.3046875" style="1" customWidth="1"/>
+    <col min="15" max="15" width="18.15234375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.15234375" style="1" customWidth="1"/>
+    <col min="17" max="17" width="56.69140625" style="1" customWidth="1"/>
+    <col min="18" max="16384" width="40.69140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" s="3" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:19" s="3" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A1" s="4" t="s">
         <v>26</v>
       </c>
@@ -768,7 +771,7 @@
       <c r="R1" s="1"/>
       <c r="S1" s="1"/>
     </row>
-    <row r="2" spans="1:19" s="3" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:19" s="3" customFormat="1" ht="29.15" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -803,7 +806,7 @@
       <c r="R2" s="1"/>
       <c r="S2" s="1"/>
     </row>
-    <row r="3" spans="1:19" s="3" customFormat="1" ht="75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:19" s="3" customFormat="1" ht="72.900000000000006" x14ac:dyDescent="0.4">
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
@@ -838,7 +841,7 @@
       <c r="R3" s="1"/>
       <c r="S3" s="1"/>
     </row>
-    <row r="4" spans="1:19" s="3" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:19" s="3" customFormat="1" ht="58.3" x14ac:dyDescent="0.4">
       <c r="A4" s="1" t="s">
         <v>0</v>
       </c>
@@ -873,7 +876,7 @@
       <c r="R4" s="1"/>
       <c r="S4" s="1"/>
     </row>
-    <row r="5" spans="1:19" ht="120" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:19" ht="116.6" x14ac:dyDescent="0.4">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
@@ -893,7 +896,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="6" spans="1:19" ht="30" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:19" ht="29.15" x14ac:dyDescent="0.4">
       <c r="A6" s="1" t="s">
         <v>0</v>
       </c>
@@ -916,7 +919,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="7" spans="1:19" s="3" customFormat="1" ht="120" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:19" s="3" customFormat="1" ht="116.6" x14ac:dyDescent="0.4">
       <c r="A7" s="1" t="s">
         <v>0</v>
       </c>
@@ -951,7 +954,7 @@
       <c r="R7" s="1"/>
       <c r="S7" s="1"/>
     </row>
-    <row r="8" spans="1:19" s="3" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:19" s="3" customFormat="1" ht="43.75" x14ac:dyDescent="0.4">
       <c r="A8" s="1" t="s">
         <v>0</v>
       </c>
@@ -984,7 +987,7 @@
       <c r="R8" s="1"/>
       <c r="S8" s="1"/>
     </row>
-    <row r="9" spans="1:19" s="3" customFormat="1" ht="90" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:19" s="3" customFormat="1" ht="87.45" x14ac:dyDescent="0.4">
       <c r="A9" s="1" t="s">
         <v>0</v>
       </c>
@@ -1033,7 +1036,7 @@
       <c r="R9" s="1"/>
       <c r="S9" s="1"/>
     </row>
-    <row r="10" spans="1:19" s="3" customFormat="1" ht="90" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:19" s="3" customFormat="1" ht="87.45" x14ac:dyDescent="0.4">
       <c r="A10" s="1" t="s">
         <v>0</v>
       </c>
@@ -1080,7 +1083,7 @@
       <c r="R10" s="1"/>
       <c r="S10" s="1"/>
     </row>
-    <row r="11" spans="1:19" s="3" customFormat="1" ht="90" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:19" s="3" customFormat="1" ht="87.45" x14ac:dyDescent="0.4">
       <c r="A11" s="1" t="s">
         <v>0</v>
       </c>
@@ -1129,7 +1132,7 @@
       <c r="R11" s="1"/>
       <c r="S11" s="1"/>
     </row>
-    <row r="12" spans="1:19" s="3" customFormat="1" ht="90" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:19" s="3" customFormat="1" ht="87.45" x14ac:dyDescent="0.4">
       <c r="A12" s="1" t="s">
         <v>0</v>
       </c>
@@ -1176,7 +1179,7 @@
       <c r="R12" s="1"/>
       <c r="S12" s="1"/>
     </row>
-    <row r="13" spans="1:19" s="3" customFormat="1" ht="90" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:19" s="3" customFormat="1" ht="87.45" x14ac:dyDescent="0.4">
       <c r="A13" s="1" t="s">
         <v>0</v>
       </c>
@@ -1225,7 +1228,7 @@
       <c r="R13" s="1"/>
       <c r="S13" s="1"/>
     </row>
-    <row r="14" spans="1:19" s="3" customFormat="1" ht="90" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:19" s="3" customFormat="1" ht="87.45" x14ac:dyDescent="0.4">
       <c r="A14" s="1" t="s">
         <v>0</v>
       </c>
@@ -1274,7 +1277,7 @@
       <c r="R14" s="1"/>
       <c r="S14" s="1"/>
     </row>
-    <row r="15" spans="1:19" s="3" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:19" s="3" customFormat="1" ht="29.15" x14ac:dyDescent="0.4">
       <c r="A15" s="1" t="s">
         <v>0</v>
       </c>
@@ -1311,7 +1314,7 @@
       <c r="R15" s="1"/>
       <c r="S15" s="1"/>
     </row>
-    <row r="16" spans="1:19" s="3" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:19" s="3" customFormat="1" ht="29.15" x14ac:dyDescent="0.4">
       <c r="A16" s="1" t="s">
         <v>0</v>
       </c>
@@ -1360,7 +1363,7 @@
       <c r="R16" s="1"/>
       <c r="S16" s="1"/>
     </row>
-    <row r="17" spans="1:19" s="3" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:19" s="3" customFormat="1" ht="29.15" x14ac:dyDescent="0.4">
       <c r="A17" s="1" t="s">
         <v>0</v>
       </c>
@@ -1409,8 +1412,48 @@
       <c r="R17" s="1"/>
       <c r="S17" s="1"/>
     </row>
-    <row r="18" spans="1:19" s="3" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="19" spans="1:19" s="3" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="18" spans="1:19" s="3" customFormat="1" ht="29.15" x14ac:dyDescent="0.4">
+      <c r="A18" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I18" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="M18" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="N18" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="O18" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="P18" s="3" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="19" spans="1:19" s="3" customFormat="1" x14ac:dyDescent="0.4"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/curation/draft/package16/R16_BC_updates.xlsx
+++ b/curation/draft/package16/R16_BC_updates.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cdisc-my.sharepoint.com/personal/jchason_cdisc_org/Documents/Work/CDISC/Biomedical Concepts/BCs for RE/files to send/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\_github\cdisc-org\COSMoS\curation\draft\package16\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8F5E3FC9-21B2-4A73-A801-FA9923351BFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC151E96-9989-4641-93E4-C228144DBDFB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="16663" windowHeight="9772" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BC_Updates" sheetId="1" r:id="rId1"/>
@@ -27,9 +27,6 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="195" uniqueCount="92">
   <si>
-    <t>update to released</t>
-  </si>
-  <si>
     <t>Flow Rate</t>
   </si>
   <si>
@@ -301,6 +298,9 @@
   </si>
   <si>
     <t>Respiratory System Findings</t>
+  </si>
+  <si>
+    <t>R16</t>
   </si>
 </sst>
 </file>
@@ -694,106 +694,106 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:S19"/>
-  <sheetFormatPr defaultColWidth="40.69140625" defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="40.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="16.3828125" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="28.3046875" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.84375" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.3046875" style="1" customWidth="1"/>
-    <col min="5" max="5" width="13.53515625" style="1" customWidth="1"/>
-    <col min="6" max="6" width="40.69140625" style="1" customWidth="1"/>
-    <col min="7" max="7" width="39.53515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.3046875" style="1" customWidth="1"/>
-    <col min="9" max="9" width="40.69140625" style="1" customWidth="1"/>
-    <col min="10" max="10" width="9.84375" style="1" customWidth="1"/>
-    <col min="11" max="11" width="13.53515625" style="1" customWidth="1"/>
-    <col min="12" max="12" width="6.69140625" style="1" customWidth="1"/>
-    <col min="13" max="13" width="6.84375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="15.3046875" style="1" customWidth="1"/>
-    <col min="15" max="15" width="18.15234375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.15234375" style="1" customWidth="1"/>
-    <col min="17" max="17" width="56.69140625" style="1" customWidth="1"/>
-    <col min="18" max="16384" width="40.69140625" style="1"/>
+    <col min="1" max="1" width="16.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.28515625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="13.5703125" style="1" customWidth="1"/>
+    <col min="6" max="6" width="40.7109375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="39.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.28515625" style="1" customWidth="1"/>
+    <col min="9" max="9" width="40.7109375" style="1" customWidth="1"/>
+    <col min="10" max="10" width="9.85546875" style="1" customWidth="1"/>
+    <col min="11" max="11" width="13.5703125" style="1" customWidth="1"/>
+    <col min="12" max="12" width="6.7109375" style="1" customWidth="1"/>
+    <col min="13" max="13" width="6.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="15.28515625" style="1" customWidth="1"/>
+    <col min="15" max="15" width="18.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.140625" style="1" customWidth="1"/>
+    <col min="17" max="17" width="56.7109375" style="1" customWidth="1"/>
+    <col min="18" max="16384" width="40.7109375" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" s="3" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:19" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="B1" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="C1" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="D1" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="E1" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="F1" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="G1" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="H1" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="I1" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="I1" s="4" t="s">
+      <c r="J1" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="J1" s="4" t="s">
+      <c r="K1" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="K1" s="4" t="s">
+      <c r="L1" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="L1" s="4" t="s">
+      <c r="M1" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="M1" s="5" t="s">
+      <c r="N1" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="N1" s="5" t="s">
+      <c r="O1" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="O1" s="5" t="s">
+      <c r="P1" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="P1" s="5" t="s">
+      <c r="Q1" s="5" t="s">
         <v>41</v>
-      </c>
-      <c r="Q1" s="5" t="s">
-        <v>42</v>
       </c>
       <c r="R1" s="1"/>
       <c r="S1" s="1"/>
     </row>
-    <row r="2" spans="1:19" s="3" customFormat="1" ht="29.15" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:19" s="3" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="C2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="1" t="s">
-        <v>2</v>
-      </c>
       <c r="D2" s="1" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E2" s="1"/>
       <c r="F2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="G2" s="1" t="s">
         <v>3</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>4</v>
       </c>
       <c r="H2" s="1"/>
       <c r="I2" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J2" s="1"/>
       <c r="K2" s="1"/>
@@ -806,29 +806,29 @@
       <c r="R2" s="1"/>
       <c r="S2" s="1"/>
     </row>
-    <row r="3" spans="1:19" s="3" customFormat="1" ht="72.900000000000006" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:19" s="3" customFormat="1" ht="75" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>0</v>
+        <v>91</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="C3" s="1" t="s">
-        <v>44</v>
-      </c>
       <c r="D3" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E3" s="1"/>
       <c r="F3" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="G3" s="1" t="s">
         <v>45</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>46</v>
       </c>
       <c r="H3" s="1"/>
       <c r="I3" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="J3" s="1"/>
       <c r="K3" s="1"/>
@@ -841,29 +841,29 @@
       <c r="R3" s="1"/>
       <c r="S3" s="1"/>
     </row>
-    <row r="4" spans="1:19" s="3" customFormat="1" ht="58.3" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:19" s="3" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>0</v>
+        <v>91</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E4" s="1"/>
       <c r="F4" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="G4" s="1" t="s">
         <v>49</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>50</v>
       </c>
       <c r="H4" s="1"/>
       <c r="I4" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="J4" s="1"/>
       <c r="K4" s="1"/>
@@ -876,72 +876,72 @@
       <c r="R4" s="1"/>
       <c r="S4" s="1"/>
     </row>
-    <row r="5" spans="1:19" ht="116.6" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:19" ht="120" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>0</v>
+        <v>91</v>
       </c>
       <c r="B5" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="C5" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="D5" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="F5" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="D5" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="F5" s="1" t="s">
+      <c r="I5" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="I5" s="1" t="s">
+    </row>
+    <row r="6" spans="1:19" ht="30" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="B6" s="1" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="6" spans="1:19" ht="29.15" x14ac:dyDescent="0.4">
-      <c r="A6" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B6" s="1" t="s">
+      <c r="C6" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="D6" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="F6" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="D6" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="F6" s="1" t="s">
+      <c r="G6" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="G6" s="1" t="s">
+      <c r="I6" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="I6" s="1" t="s">
+    </row>
+    <row r="7" spans="1:19" s="3" customFormat="1" ht="120" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="B7" s="1" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="7" spans="1:19" s="3" customFormat="1" ht="116.6" x14ac:dyDescent="0.4">
-      <c r="A7" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B7" s="1" t="s">
+      <c r="C7" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="C7" s="1" t="s">
-        <v>62</v>
-      </c>
       <c r="D7" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E7" s="1"/>
       <c r="F7" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="G7" s="1" t="s">
         <v>63</v>
-      </c>
-      <c r="G7" s="1" t="s">
-        <v>64</v>
       </c>
       <c r="H7" s="1"/>
       <c r="I7" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="J7" s="1"/>
       <c r="K7" s="1"/>
@@ -954,27 +954,27 @@
       <c r="R7" s="1"/>
       <c r="S7" s="1"/>
     </row>
-    <row r="8" spans="1:19" s="3" customFormat="1" ht="43.75" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:19" s="3" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>0</v>
+        <v>91</v>
       </c>
       <c r="B8" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="C8" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="C8" s="1" t="s">
-        <v>67</v>
-      </c>
       <c r="D8" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E8" s="1"/>
       <c r="F8" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G8" s="1"/>
       <c r="H8" s="1"/>
       <c r="I8" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="J8" s="1"/>
       <c r="K8" s="1"/>
@@ -987,321 +987,321 @@
       <c r="R8" s="1"/>
       <c r="S8" s="1"/>
     </row>
-    <row r="9" spans="1:19" s="3" customFormat="1" ht="87.45" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:19" s="3" customFormat="1" ht="90" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>0</v>
+        <v>91</v>
       </c>
       <c r="B9" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="C9" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="C9" s="1" t="s">
+      <c r="D9" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="E9" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="D9" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="E9" s="1" t="s">
+      <c r="F9" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="F9" s="1" t="s">
+      <c r="G9" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="G9" s="1" t="s">
+      <c r="H9" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="H9" s="1" t="s">
+      <c r="I9" s="1" t="s">
         <v>75</v>
-      </c>
-      <c r="I9" s="1" t="s">
-        <v>76</v>
       </c>
       <c r="J9" s="1"/>
       <c r="K9" s="1"/>
       <c r="L9" s="1"/>
       <c r="M9" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="N9" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="O9" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="N9" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="O9" s="1" t="s">
+      <c r="P9" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q9" s="1" t="s">
         <v>78</v>
-      </c>
-      <c r="P9" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q9" s="1" t="s">
-        <v>79</v>
       </c>
       <c r="R9" s="1"/>
       <c r="S9" s="1"/>
     </row>
-    <row r="10" spans="1:19" s="3" customFormat="1" ht="87.45" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:19" s="3" customFormat="1" ht="90" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>0</v>
+        <v>91</v>
       </c>
       <c r="B10" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="C10" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="C10" s="1" t="s">
+      <c r="D10" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="E10" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="D10" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="E10" s="1" t="s">
+      <c r="F10" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="F10" s="1" t="s">
+      <c r="G10" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="G10" s="1" t="s">
+      <c r="H10" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="H10" s="1" t="s">
+      <c r="I10" s="1" t="s">
         <v>75</v>
-      </c>
-      <c r="I10" s="1" t="s">
-        <v>76</v>
       </c>
       <c r="J10" s="1"/>
       <c r="K10" s="1"/>
       <c r="L10" s="1"/>
       <c r="M10" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="N10" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="O10" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="N10" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="O10" s="1" t="s">
+      <c r="P10" s="1" t="s">
         <v>81</v>
-      </c>
-      <c r="P10" s="1" t="s">
-        <v>82</v>
       </c>
       <c r="Q10" s="1"/>
       <c r="R10" s="1"/>
       <c r="S10" s="1"/>
     </row>
-    <row r="11" spans="1:19" s="3" customFormat="1" ht="87.45" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:19" s="3" customFormat="1" ht="90" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>0</v>
+        <v>91</v>
       </c>
       <c r="B11" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="C11" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="C11" s="1" t="s">
+      <c r="D11" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="E11" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="D11" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="E11" s="1" t="s">
+      <c r="F11" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="F11" s="1" t="s">
+      <c r="G11" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="G11" s="1" t="s">
+      <c r="H11" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="H11" s="1" t="s">
+      <c r="I11" s="1" t="s">
         <v>75</v>
-      </c>
-      <c r="I11" s="1" t="s">
-        <v>76</v>
       </c>
       <c r="J11" s="1"/>
       <c r="K11" s="1"/>
       <c r="L11" s="1"/>
       <c r="M11" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="N11" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="O11" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="N11" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="O11" s="1" t="s">
+      <c r="P11" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q11" s="1" t="s">
         <v>84</v>
-      </c>
-      <c r="P11" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q11" s="1" t="s">
-        <v>85</v>
       </c>
       <c r="R11" s="1"/>
       <c r="S11" s="1"/>
     </row>
-    <row r="12" spans="1:19" s="3" customFormat="1" ht="87.45" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:19" s="3" customFormat="1" ht="90" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>0</v>
+        <v>91</v>
       </c>
       <c r="B12" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="C12" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="C12" s="1" t="s">
+      <c r="D12" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="E12" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="D12" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="E12" s="1" t="s">
+      <c r="F12" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="F12" s="1" t="s">
+      <c r="G12" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="G12" s="1" t="s">
+      <c r="H12" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="H12" s="1" t="s">
+      <c r="I12" s="1" t="s">
         <v>75</v>
-      </c>
-      <c r="I12" s="1" t="s">
-        <v>76</v>
       </c>
       <c r="J12" s="1"/>
       <c r="K12" s="1"/>
       <c r="L12" s="1"/>
       <c r="M12" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="N12" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="O12" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="N12" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="O12" s="1" t="s">
-        <v>20</v>
-      </c>
       <c r="P12" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="Q12" s="1"/>
       <c r="R12" s="1"/>
       <c r="S12" s="1"/>
     </row>
-    <row r="13" spans="1:19" s="3" customFormat="1" ht="87.45" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:19" s="3" customFormat="1" ht="90" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>0</v>
+        <v>91</v>
       </c>
       <c r="B13" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="C13" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="C13" s="1" t="s">
+      <c r="D13" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="E13" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="D13" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="E13" s="1" t="s">
+      <c r="F13" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="F13" s="1" t="s">
+      <c r="G13" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="G13" s="1" t="s">
+      <c r="H13" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="H13" s="1" t="s">
+      <c r="I13" s="1" t="s">
         <v>75</v>
-      </c>
-      <c r="I13" s="1" t="s">
-        <v>76</v>
       </c>
       <c r="J13" s="1"/>
       <c r="K13" s="1"/>
       <c r="L13" s="1"/>
       <c r="M13" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="N13" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="O13" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="N13" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="O13" s="1" t="s">
+      <c r="P13" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q13" s="1" t="s">
         <v>88</v>
-      </c>
-      <c r="P13" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q13" s="1" t="s">
-        <v>89</v>
       </c>
       <c r="R13" s="1"/>
       <c r="S13" s="1"/>
     </row>
-    <row r="14" spans="1:19" s="3" customFormat="1" ht="87.45" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:19" s="3" customFormat="1" ht="90" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>0</v>
+        <v>91</v>
       </c>
       <c r="B14" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="C14" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="C14" s="1" t="s">
+      <c r="D14" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="E14" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="D14" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="E14" s="1" t="s">
+      <c r="F14" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="F14" s="1" t="s">
+      <c r="G14" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="G14" s="1" t="s">
+      <c r="H14" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="H14" s="1" t="s">
+      <c r="I14" s="1" t="s">
         <v>75</v>
-      </c>
-      <c r="I14" s="1" t="s">
-        <v>76</v>
       </c>
       <c r="J14" s="1"/>
       <c r="K14" s="1"/>
       <c r="L14" s="1"/>
       <c r="M14" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="N14" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="O14" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="N14" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="O14" s="1" t="s">
-        <v>24</v>
-      </c>
       <c r="P14" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="Q14" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="R14" s="1"/>
       <c r="S14" s="1"/>
     </row>
-    <row r="15" spans="1:19" s="3" customFormat="1" ht="29.15" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:19" s="3" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>0</v>
+        <v>91</v>
       </c>
       <c r="B15" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C15" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C15" s="1" t="s">
+      <c r="D15" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E15" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D15" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="E15" s="1" t="s">
+      <c r="F15" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="F15" s="1" t="s">
+      <c r="G15" s="1" t="s">
         <v>9</v>
-      </c>
-      <c r="G15" s="1" t="s">
-        <v>10</v>
       </c>
       <c r="H15" s="1"/>
       <c r="I15" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J15" s="1"/>
       <c r="K15" s="1"/>
@@ -1314,146 +1314,146 @@
       <c r="R15" s="1"/>
       <c r="S15" s="1"/>
     </row>
-    <row r="16" spans="1:19" s="3" customFormat="1" ht="29.15" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:19" s="3" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>0</v>
+        <v>91</v>
       </c>
       <c r="B16" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C16" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C16" s="1" t="s">
+      <c r="D16" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E16" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D16" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="E16" s="1" t="s">
+      <c r="F16" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="F16" s="1" t="s">
+      <c r="G16" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="G16" s="1" t="s">
+      <c r="H16" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="H16" s="1" t="s">
+      <c r="I16" s="1" t="s">
         <v>17</v>
-      </c>
-      <c r="I16" s="1" t="s">
-        <v>18</v>
       </c>
       <c r="J16" s="1"/>
       <c r="K16" s="1"/>
       <c r="L16" s="1"/>
       <c r="M16" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="N16" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="O16" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="N16" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="O16" s="1" t="s">
+      <c r="P16" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="P16" s="1" t="s">
+      <c r="Q16" s="1" t="s">
         <v>21</v>
-      </c>
-      <c r="Q16" s="1" t="s">
-        <v>22</v>
       </c>
       <c r="R16" s="1"/>
       <c r="S16" s="1"/>
     </row>
-    <row r="17" spans="1:19" s="3" customFormat="1" ht="29.15" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:19" s="3" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>0</v>
+        <v>91</v>
       </c>
       <c r="B17" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C17" s="1" t="s">
+      <c r="D17" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E17" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D17" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="E17" s="1" t="s">
+      <c r="F17" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="F17" s="1" t="s">
+      <c r="G17" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="G17" s="1" t="s">
+      <c r="H17" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="H17" s="1" t="s">
+      <c r="I17" s="1" t="s">
         <v>17</v>
-      </c>
-      <c r="I17" s="1" t="s">
-        <v>18</v>
       </c>
       <c r="J17" s="1"/>
       <c r="K17" s="1"/>
       <c r="L17" s="1"/>
       <c r="M17" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="N17" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="O17" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="N17" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="O17" s="1" t="s">
+      <c r="P17" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q17" s="1" t="s">
         <v>24</v>
-      </c>
-      <c r="P17" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q17" s="1" t="s">
-        <v>25</v>
       </c>
       <c r="R17" s="1"/>
       <c r="S17" s="1"/>
     </row>
-    <row r="18" spans="1:19" s="3" customFormat="1" ht="29.15" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:19" s="3" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>0</v>
+        <v>91</v>
       </c>
       <c r="B18" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C18" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C18" s="3" t="s">
+      <c r="D18" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E18" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="D18" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="E18" s="3" t="s">
-        <v>14</v>
-      </c>
       <c r="F18" s="3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="G18" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="H18" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="H18" s="3" t="s">
+      <c r="I18" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="I18" s="3" t="s">
-        <v>18</v>
-      </c>
       <c r="M18" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="N18" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="O18" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="N18" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="O18" s="3" t="s">
+      <c r="P18" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="P18" s="3" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="19" spans="1:19" s="3" customFormat="1" x14ac:dyDescent="0.4"/>
+    </row>
+    <row r="19" spans="1:19" s="3" customFormat="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/curation/draft/package16/R16_BC_updates.xlsx
+++ b/curation/draft/package16/R16_BC_updates.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\_github\cdisc-org\COSMoS\curation\draft\package16\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC151E96-9989-4641-93E4-C228144DBDFB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B72040B3-7815-4DA6-8382-19AC79689290}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="915" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BC_Updates" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="195" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="356" uniqueCount="120">
   <si>
     <t>Flow Rate</t>
   </si>
@@ -301,6 +301,90 @@
   </si>
   <si>
     <t>R16</t>
+  </si>
+  <si>
+    <t>Partial Pressure Arterial Oxygen to Fraction Inspired Oxygen Ratio Measurement</t>
+  </si>
+  <si>
+    <t>C119293</t>
+  </si>
+  <si>
+    <t>Laboratory Tests;Blood Oxygen Levels; Respiratory System Findings</t>
+  </si>
+  <si>
+    <t>Horowitz Index;Carrico index;P/F ratio;Partial Pressure Arterial Oxygen to Fraction Inspired Oxygen Ratio Measurement;PO2FIO2;PAO2/FIO2;PP Arterial O2/Fraction Inspired O2</t>
+  </si>
+  <si>
+    <t>The determination of the ratio of the pressure of oxygen dissolved in arterial blood to the percentage oxygen of an inhaled mixture of gasses in a biological specimen.</t>
+  </si>
+  <si>
+    <t>https://loinc.org</t>
+  </si>
+  <si>
+    <t>LOINC</t>
+  </si>
+  <si>
+    <t>50984-4</t>
+  </si>
+  <si>
+    <t>C49669</t>
+  </si>
+  <si>
+    <t>Unit of Pressure</t>
+  </si>
+  <si>
+    <t>mmHg</t>
+  </si>
+  <si>
+    <t>C70713</t>
+  </si>
+  <si>
+    <t>Biospecimen Type</t>
+  </si>
+  <si>
+    <t>Arterial Blood</t>
+  </si>
+  <si>
+    <t>decimal</t>
+  </si>
+  <si>
+    <t>Blood Flow Rate</t>
+  </si>
+  <si>
+    <t>C94866</t>
+  </si>
+  <si>
+    <t>Findings;Clinical Test Result;Renal Function Tests;Urinary System Findings; Respiratory System Findings</t>
+  </si>
+  <si>
+    <t>Blood Flow Rate;BLDFLRT</t>
+  </si>
+  <si>
+    <t>The volume of blood per unit time passing through a specified location, such as a point in a blood vessel or an entire organ. Units are ml/sec.</t>
+  </si>
+  <si>
+    <t>Kidney</t>
+  </si>
+  <si>
+    <t>Right;Left</t>
+  </si>
+  <si>
+    <t>C48568</t>
+  </si>
+  <si>
+    <t>Unit of Volumetric Flow Rate</t>
+  </si>
+  <si>
+    <t>mL/s;L/min;mL/min;L/h</t>
+  </si>
+  <si>
+    <t>C48564</t>
+  </si>
+  <si>
+    <t>Unit of Linear Velocity</t>
+  </si>
+  <si>
+    <t>cm/s</t>
   </si>
 </sst>
 </file>
@@ -693,7 +777,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:S19"/>
+  <dimension ref="A1:S31"/>
   <sheetFormatPr defaultColWidth="40.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16.42578125" style="1" bestFit="1" customWidth="1"/>
@@ -1453,7 +1537,571 @@
         <v>81</v>
       </c>
     </row>
-    <row r="19" spans="1:19" s="3" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="19" spans="1:19" s="3" customFormat="1" ht="75" x14ac:dyDescent="0.25">
+      <c r="A19" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="B19" t="s">
+        <v>92</v>
+      </c>
+      <c r="C19" t="s">
+        <v>93</v>
+      </c>
+      <c r="D19" t="s">
+        <v>93</v>
+      </c>
+      <c r="E19" t="s">
+        <v>6</v>
+      </c>
+      <c r="F19" t="s">
+        <v>94</v>
+      </c>
+      <c r="G19" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="H19" t="s">
+        <v>74</v>
+      </c>
+      <c r="I19" t="s">
+        <v>96</v>
+      </c>
+      <c r="J19" t="s">
+        <v>97</v>
+      </c>
+      <c r="K19" t="s">
+        <v>98</v>
+      </c>
+      <c r="L19" t="s">
+        <v>99</v>
+      </c>
+      <c r="M19" t="s">
+        <v>100</v>
+      </c>
+      <c r="N19" t="s">
+        <v>100</v>
+      </c>
+      <c r="O19" t="s">
+        <v>101</v>
+      </c>
+      <c r="P19" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q19" s="1" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="20" spans="1:19" ht="75" x14ac:dyDescent="0.25">
+      <c r="A20" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="B20" t="s">
+        <v>92</v>
+      </c>
+      <c r="C20" t="s">
+        <v>93</v>
+      </c>
+      <c r="D20" t="s">
+        <v>93</v>
+      </c>
+      <c r="E20" t="s">
+        <v>6</v>
+      </c>
+      <c r="F20" t="s">
+        <v>94</v>
+      </c>
+      <c r="G20" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="H20" t="s">
+        <v>74</v>
+      </c>
+      <c r="I20" t="s">
+        <v>96</v>
+      </c>
+      <c r="J20" t="s">
+        <v>97</v>
+      </c>
+      <c r="K20" t="s">
+        <v>98</v>
+      </c>
+      <c r="L20" t="s">
+        <v>99</v>
+      </c>
+      <c r="M20" t="s">
+        <v>103</v>
+      </c>
+      <c r="N20" t="s">
+        <v>103</v>
+      </c>
+      <c r="O20" t="s">
+        <v>104</v>
+      </c>
+      <c r="P20" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q20" s="1" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="21" spans="1:19" ht="75" x14ac:dyDescent="0.25">
+      <c r="A21" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="B21" t="s">
+        <v>92</v>
+      </c>
+      <c r="C21" t="s">
+        <v>93</v>
+      </c>
+      <c r="D21" t="s">
+        <v>93</v>
+      </c>
+      <c r="E21" t="s">
+        <v>6</v>
+      </c>
+      <c r="F21" t="s">
+        <v>94</v>
+      </c>
+      <c r="G21" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="H21" t="s">
+        <v>74</v>
+      </c>
+      <c r="I21" t="s">
+        <v>96</v>
+      </c>
+      <c r="J21" t="s">
+        <v>97</v>
+      </c>
+      <c r="K21" t="s">
+        <v>98</v>
+      </c>
+      <c r="L21" t="s">
+        <v>99</v>
+      </c>
+      <c r="M21" t="s">
+        <v>18</v>
+      </c>
+      <c r="N21" t="s">
+        <v>18</v>
+      </c>
+      <c r="O21" t="s">
+        <v>19</v>
+      </c>
+      <c r="P21" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="22" spans="1:19" ht="75" x14ac:dyDescent="0.25">
+      <c r="A22" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="B22" t="s">
+        <v>92</v>
+      </c>
+      <c r="C22" t="s">
+        <v>93</v>
+      </c>
+      <c r="D22" t="s">
+        <v>93</v>
+      </c>
+      <c r="E22" t="s">
+        <v>6</v>
+      </c>
+      <c r="F22" t="s">
+        <v>94</v>
+      </c>
+      <c r="G22" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="H22" t="s">
+        <v>74</v>
+      </c>
+      <c r="I22" t="s">
+        <v>96</v>
+      </c>
+      <c r="J22" t="s">
+        <v>97</v>
+      </c>
+      <c r="K22" t="s">
+        <v>98</v>
+      </c>
+      <c r="L22" t="s">
+        <v>99</v>
+      </c>
+      <c r="M22" t="s">
+        <v>79</v>
+      </c>
+      <c r="N22" t="s">
+        <v>79</v>
+      </c>
+      <c r="O22" t="s">
+        <v>80</v>
+      </c>
+      <c r="P22" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="23" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A23"/>
+      <c r="B23"/>
+      <c r="C23"/>
+      <c r="D23"/>
+      <c r="E23"/>
+      <c r="F23"/>
+      <c r="G23"/>
+      <c r="H23"/>
+      <c r="I23"/>
+      <c r="J23"/>
+      <c r="K23"/>
+      <c r="L23"/>
+      <c r="M23"/>
+      <c r="N23"/>
+      <c r="O23"/>
+      <c r="P23"/>
+    </row>
+    <row r="24" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A24"/>
+      <c r="B24"/>
+      <c r="C24"/>
+      <c r="D24"/>
+      <c r="E24"/>
+      <c r="F24"/>
+      <c r="G24"/>
+      <c r="H24"/>
+      <c r="I24"/>
+      <c r="J24"/>
+      <c r="K24"/>
+      <c r="L24"/>
+      <c r="M24"/>
+      <c r="N24"/>
+      <c r="O24"/>
+      <c r="P24"/>
+    </row>
+    <row r="25" spans="1:19" ht="45" x14ac:dyDescent="0.25">
+      <c r="A25" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="B25" t="s">
+        <v>107</v>
+      </c>
+      <c r="C25" t="s">
+        <v>108</v>
+      </c>
+      <c r="D25" t="s">
+        <v>108</v>
+      </c>
+      <c r="E25" t="s">
+        <v>1</v>
+      </c>
+      <c r="F25" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="G25" t="s">
+        <v>110</v>
+      </c>
+      <c r="H25" t="s">
+        <v>74</v>
+      </c>
+      <c r="I25" t="s">
+        <v>111</v>
+      </c>
+      <c r="J25"/>
+      <c r="K25"/>
+      <c r="L25"/>
+      <c r="M25" t="s">
+        <v>76</v>
+      </c>
+      <c r="N25" t="s">
+        <v>76</v>
+      </c>
+      <c r="O25" t="s">
+        <v>77</v>
+      </c>
+      <c r="P25" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q25" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="26" spans="1:19" ht="45" x14ac:dyDescent="0.25">
+      <c r="A26" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="B26" t="s">
+        <v>107</v>
+      </c>
+      <c r="C26" t="s">
+        <v>108</v>
+      </c>
+      <c r="D26" t="s">
+        <v>108</v>
+      </c>
+      <c r="E26" t="s">
+        <v>1</v>
+      </c>
+      <c r="F26" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="G26" t="s">
+        <v>110</v>
+      </c>
+      <c r="H26" t="s">
+        <v>74</v>
+      </c>
+      <c r="I26" t="s">
+        <v>111</v>
+      </c>
+      <c r="J26"/>
+      <c r="K26"/>
+      <c r="L26"/>
+      <c r="M26" t="s">
+        <v>79</v>
+      </c>
+      <c r="N26" t="s">
+        <v>79</v>
+      </c>
+      <c r="O26" t="s">
+        <v>80</v>
+      </c>
+      <c r="P26" t="s">
+        <v>81</v>
+      </c>
+      <c r="Q26"/>
+    </row>
+    <row r="27" spans="1:19" ht="45" x14ac:dyDescent="0.25">
+      <c r="A27" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="B27" t="s">
+        <v>107</v>
+      </c>
+      <c r="C27" t="s">
+        <v>108</v>
+      </c>
+      <c r="D27" t="s">
+        <v>108</v>
+      </c>
+      <c r="E27" t="s">
+        <v>1</v>
+      </c>
+      <c r="F27" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="G27" t="s">
+        <v>110</v>
+      </c>
+      <c r="H27" t="s">
+        <v>74</v>
+      </c>
+      <c r="I27" t="s">
+        <v>111</v>
+      </c>
+      <c r="J27"/>
+      <c r="K27"/>
+      <c r="L27"/>
+      <c r="M27" t="s">
+        <v>82</v>
+      </c>
+      <c r="N27" t="s">
+        <v>82</v>
+      </c>
+      <c r="O27" t="s">
+        <v>83</v>
+      </c>
+      <c r="P27" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q27" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="28" spans="1:19" ht="45" x14ac:dyDescent="0.25">
+      <c r="A28" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="B28" t="s">
+        <v>107</v>
+      </c>
+      <c r="C28" t="s">
+        <v>108</v>
+      </c>
+      <c r="D28" t="s">
+        <v>108</v>
+      </c>
+      <c r="E28" t="s">
+        <v>1</v>
+      </c>
+      <c r="F28" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="G28" t="s">
+        <v>110</v>
+      </c>
+      <c r="H28" t="s">
+        <v>74</v>
+      </c>
+      <c r="I28" t="s">
+        <v>111</v>
+      </c>
+      <c r="J28"/>
+      <c r="K28"/>
+      <c r="L28"/>
+      <c r="M28" t="s">
+        <v>18</v>
+      </c>
+      <c r="N28" t="s">
+        <v>18</v>
+      </c>
+      <c r="O28" t="s">
+        <v>19</v>
+      </c>
+      <c r="P28" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q28"/>
+    </row>
+    <row r="29" spans="1:19" ht="45" x14ac:dyDescent="0.25">
+      <c r="A29" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="B29" t="s">
+        <v>107</v>
+      </c>
+      <c r="C29" t="s">
+        <v>108</v>
+      </c>
+      <c r="D29" t="s">
+        <v>108</v>
+      </c>
+      <c r="E29" t="s">
+        <v>1</v>
+      </c>
+      <c r="F29" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="G29" t="s">
+        <v>110</v>
+      </c>
+      <c r="H29" t="s">
+        <v>74</v>
+      </c>
+      <c r="I29" t="s">
+        <v>111</v>
+      </c>
+      <c r="J29"/>
+      <c r="K29"/>
+      <c r="L29"/>
+      <c r="M29" t="s">
+        <v>22</v>
+      </c>
+      <c r="N29" t="s">
+        <v>22</v>
+      </c>
+      <c r="O29" t="s">
+        <v>23</v>
+      </c>
+      <c r="P29" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q29"/>
+    </row>
+    <row r="30" spans="1:19" ht="45" x14ac:dyDescent="0.25">
+      <c r="A30" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="B30" t="s">
+        <v>107</v>
+      </c>
+      <c r="C30" t="s">
+        <v>108</v>
+      </c>
+      <c r="D30" t="s">
+        <v>108</v>
+      </c>
+      <c r="E30" t="s">
+        <v>1</v>
+      </c>
+      <c r="F30" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="G30" t="s">
+        <v>110</v>
+      </c>
+      <c r="H30" t="s">
+        <v>74</v>
+      </c>
+      <c r="I30" t="s">
+        <v>111</v>
+      </c>
+      <c r="J30"/>
+      <c r="K30"/>
+      <c r="L30"/>
+      <c r="M30" t="s">
+        <v>114</v>
+      </c>
+      <c r="N30" t="s">
+        <v>114</v>
+      </c>
+      <c r="O30" t="s">
+        <v>115</v>
+      </c>
+      <c r="P30" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q30" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="31" spans="1:19" ht="45" x14ac:dyDescent="0.25">
+      <c r="A31" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="B31" t="s">
+        <v>107</v>
+      </c>
+      <c r="C31" t="s">
+        <v>108</v>
+      </c>
+      <c r="D31" t="s">
+        <v>108</v>
+      </c>
+      <c r="E31" t="s">
+        <v>1</v>
+      </c>
+      <c r="F31" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="G31" t="s">
+        <v>110</v>
+      </c>
+      <c r="H31" t="s">
+        <v>74</v>
+      </c>
+      <c r="I31" t="s">
+        <v>111</v>
+      </c>
+      <c r="J31"/>
+      <c r="K31"/>
+      <c r="L31"/>
+      <c r="M31" t="s">
+        <v>117</v>
+      </c>
+      <c r="N31" t="s">
+        <v>117</v>
+      </c>
+      <c r="O31" t="s">
+        <v>118</v>
+      </c>
+      <c r="P31" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q31" t="s">
+        <v>119</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
